--- a/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
+++ b/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1125,6 +1125,111 @@
       <c r="G18" s="3" t="inlineStr">
         <is>
           <t>분류 체계 — Survey</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Recursive Multi-Agent Systems (RecursiveMAS)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Xiyuan Yang, Jiaru Zou, Rui Pan, Ruizhong Qiu, Pan Lu, Shizhe Diao, Jindong Jiang, Hanghang Tong, Tong Zhang, Markus J. Buehler, Jingrui He, James Zou / UIUC + Stanford + MIT + NVIDIA</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.25917</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Latent reasoning을 single model에서 multi-agent system으로 확장. RecursiveLink(Inner/Outer) 모듈로 agent 내부 latent feedback과 cross-agent latent state transfer 구현. Inner-Outer Loop 학습으로 RecursiveLink만 ~13M(0.31%) 학습. 9개 벤치마크(수학·과학·의학·검색·코드)에서 평균 +8.3%, 1.2-2.4x 가속, 34.6-75.6% 토큰 감소. Sequential/Mixture/Distillation/Deliberation 4가지 협업 패턴 검증. Theorem 4.1: latent recursion이 text recursion보다 gradient 안정성 증명.</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS 프로젝트 페이지</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Recursive Multi-Agent Systems Team</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>https://recursivemas.github.io</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS 공식 프로젝트 페이지. 아키텍처 다이어그램, 성능 결과, 코드/모델 링크 제공.</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS GitHub Repository</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS Team</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>https://github.com/RecursiveMAS/RecursiveMAS</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS 공식 코드 저장소. RecursiveLink 구현, 4가지 협업 패턴(Sequential/Mixture/Distillation/Deliberation) 학습 스크립트, HuggingFace 체크포인트 포함.</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>RecursiveMAS</t>
         </is>
       </c>
     </row>

--- a/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
+++ b/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1230,6 +1230,216 @@
       <c r="G21" s="3" t="inlineStr">
         <is>
           <t>RecursiveMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>CODI: Compressing Chain-of-Thought into Continuous Space via Self-Distillation</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Zhenyi Shen et al. / King's College London</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2502.21074</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Coconut의 GSM8K 약점(34.1% vs CoT 42.9%)을 self-distillation으로 해결. Teacher task(Explicit CoT)와 student task(Implicit CoT)를 jointly 학습하여 hidden state alignment. GPT-2에서 43.7%, LLaMA-3.2-1B에서 55.6% 달성. Coconut 대비 2.7-5.9x 속도. EMNLP 2025 발표.</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Coconut 후속</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Dynamics Within Latent Chain-of-Thought</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint) / 미공개</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.08783</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Coconut과 CODI를 causal probing과 mechanistic tracing으로 직접 분석. (1) 특정 latent step이 정답에 인과적으로 필수, (2) latent step 간 점진적 정보 전파, (3) 다중 가설 동시 유지(BFS 가설 mechanistic 확증) 발견. 결론: latent reasoning은 진짜 구조화된 reasoning을 한다.</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Latent 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Latent Chain-of-Thought? Decoding the Depth-Recurrent Transformer</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>다수 저자</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2507.02199</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Huginn-3.5B(depth-recurrent transformer)를 logit lens와 coda lens(neural variant)로 분석. Limited evidence of interpretable latent CoT. Probe 결과가 측정 방법에 따라 disagreement 큼. Recurrent depth 증가 시 marginal gain만. Coconut과 다른 아키텍처의 latent reasoning은 다른 dynamics를 가질 수 있음을 시사.</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Latent 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Latent Thinking Optimization (LTO)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>다수 저자</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.26314</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Huginn-3.5B의 latent thought에 reward signal이 자연 발생적으로 인코딩되어 있다는 발견. 작은 classifier로 latent thought만 보고 정답/오답 신뢰성 있게 예측 가능. 이를 Latent Reward Model(LRM)로 활용해 test-time에 latent thought 최적화. 다양한 reasoning task에서 일관된 향상. ICLR 2026 발표.</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Latent 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Unlocking the Black Box of Latent Reasoning: An Interpretability-Guided Approach to Intervention</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>다수 저자 / Anonymous (ACL ARR 2026 Jan)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>https://openreview.net/forum?id=VHsfDkWqkS</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Structural + Causal + Geometric probes 3종 동시 분석. Latent vector가 compressed, faithful representations of reasoning steps을 담고 있고, 초기 latent vector가 critical causal hub 역할. Training-free, decode-time intervention으로 reasoning 정확도 향상. Coconut curriculum이 stage 0부터 시작하는 이유 정당화.</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Latent 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SPAR Project — Interpreting latent reasoning: methods for understanding continuous chain-of-thought</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic 출신 mentor / SPAR Spring 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>https://sparai.org/projects/sp26/recip3J5fnlBXUyFB/</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-Spring</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic 출신 연구자가 멘토링하는 alignment-focused 프로젝트. Continuous chain-of-thought 해석 방법론 개발이 목표. 현재 진행 중, 결과 2026 하반기 예상. 해석성이 단순 트릭이 아니라 safety-critical 도전 과제로 인식되고 있음을 보여줌.</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Latent 해석</t>
         </is>
       </c>
     </row>

--- a/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
+++ b/2026-05-08-latent-reasoning/latent-reasoning-references.xlsx
@@ -484,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1440,6 +1440,496 @@
       <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Latent 해석</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Capabilities and Fundamental Limits of Latent Chain-of-Thought</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.01148</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Latent CoT의 exploration-execution trade-off를 이론적으로 증명. Symbolic Index로 decisional commitment 정량화. Curriculum learning이 distributional mismatch 때문에 이론적으로 essential함을 증명. Coconut의 ProsQA 97% vs GSM8K 34.1% 패턴을 high-vs-low certainty trade-off로 설명.</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>2026 이론</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Chain Of Thought Compression: A Theoretical Analysis (ALiCoT)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.21576</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>High-order logical dependency가 implicit CoT compression 시 exponentially decay함을 증명. Order-r Interaction 이론. ALiCoT(Aligned Implicit CoT)로 latent token 분포를 intermediate reasoning state와 align하여 54.4x speedup, explicit CoT 성능 유지. NatBool-DAG 벤치마크 도입.</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>2026 이론</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Thinking Without Words: Efficient Latent Reasoning with Abstract Chain-of-Thought</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.22709</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Continuous embedding 대신 reserved discrete abstract vocabulary 사용 (해석성 부분 회복). (i) verbal CoT masking+SFT, (ii) abstract token self-distillation 교대 학습. 11.6x 토큰 감소하면서 수학·instruction·multi-hop reasoning 성능 유지. Abstract vocabulary에 emergent power law 분포 관찰.</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>RLTT: Rewarding Latent Thought Trajectories in Looped Language Models</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.10520</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Looped LM의 internal step 전체에 reward를 분배하는 RL 방법. 표준 GRPO는 final output에만 reward라서 mismatch. Ouro-2.6B-Thinking 기반, MATH-500 +14.4%, AIME24 +16.6%, BeyondAIME +10.0% (GRPO 대비). 수학 학습만으로 비수학 도메인 전이.</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>PLaT: Latent Chain-of-Thought as Planning</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2601.21358</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning을 deterministic latent planning trajectory로 모델링, separate decoder가 text grounding. Dynamic termination (Coconut의 fixed c 값 불요). Greedy accuracy는 lower이지만 inference-time search 확장성 우수.</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>SIM-CoT: Supervised Implicit Chain-of-Thought</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Xilin Wei, Xiaoran Liu, Yuhang Zang, Xiaoyi Dong / Fudan + Shanghai AI Lab + CUHK</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2509.20317</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Auxiliary decoder로 step-level supervision (inference 시 decoder 제거). GPT-2 기준 Coconut +8.2%p, CODI +4.3%p. LLaMA 1B/3B/8B에서 +1.5~9.0%p. 8-16 implicit token까지 안정 작동 (prior methods는 collapse). ICLR 2026 발표.</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Latent Reasoning with Supervised Thinking States</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.08332</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Input 처리 도중에 thinking token 생성 (Coconut은 input 처리 후). Teacher-forcing으로 parallelizable. Natural language supervision 활용. 수학 task에서 CoT 격차 narrowing, 2-Hop QA에서 CoT 매칭 + latency 개선.</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Latent Thoughts Tuning (LT-Tuning)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.10229</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Context-Prediction-Fusion 메커니즘으로 contextual hidden state + vocabulary embedding의 predictive semantic guidance 결합. Coconut의 functional collapse(반복 사용 시 distributional mismatch) 해결.</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Inference-Time Rethinking with Latent Thought Vectors</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.06584</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Reasoning을 (continuous latent thought vector) + (decoder)로 factorize. Inference에서 Gibbs-style alternating optimization으로 latent vector 반복 개선. 0.2B 모델이 30 rethinking iteration으로 3B 모델 능가(GSM8K). Inference-time compute scaling의 새 축.</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>2026 신규 방법</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Ouro: Looped Language Models</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>ByteDance + UCSC + Princeton + CMU 외</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2510.25741</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Parameter-shared looped transformer (R4: 4 recurrent step). Standard decoder-only + entropy-regularized depth allocation. 1.4B가 4B 대등, 2.6B가 8B 대등 (2-3x parameter efficiency). 7.7T 토큰 학습 (3T base + 3T 추가 + 1.4T CoT annealing). HF 공개 (1.4B/2.6B + Thinking variants). RLTT의 base 모델.</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>2026 looped 아키텍처</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>LaRA-VLA: Latent Reasoning for Vision-Language-Action Models</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint) / ICML 2026</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2602.01166</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>VLA(Vision-Language-Action) 모델에 latent reasoning 적용. 3-stage curriculum (explicit CoT → latent reasoning → action-conditioned latent dynamics). 명시적 CoT 대비 90% latency 감소. Simulation + real-robot manipulation SOTA. ICML 2026.</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>2026 도메인 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Visual Latents Know More Than They Say: Unsilencing Latent Reasoning in MLLMs</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2605.02735</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>MLLM의 optimization pathology 발견: visual latent가 학습 중에 enriched되지만 answer prediction 시점에 systematically suppressed. 2-stage inference-time optimization (no param update): (I) query-guided contrastive alignment, (II) confidence-progression reward. 8개 벤치마크 × 4개 backbone에서 일관 개선.</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>2026 도메인 확장</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>LLM Reasoning Is Latent, Not the Chain of Thought</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Wenshuo Wang</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.15726</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Position paper. CoT가 reasoning을 충실히 드러낸다는 통념 반박. 3가지 가설 (H1: latent state trajectory가 primary, H2: surface CoT가 primary, H0: compute scaling) 비교 framework 제시. Compute-audited worked exemplars + latent intervention으로 분리. 권고: latent state dynamics를 default 연구 대상으로.</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>2026 입장</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>LongCoT: Benchmarking Long-Horizon Chain-of-Thought Reasoning</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Anonymous (Preprint)</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>https://arxiv.org/abs/2604.14140</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Long-horizon CoT 벤치마크: 2,500 expert-designed 문제, 5개 도메인 (chemistry, math, CS, chess, logic). Long-horizon = tens to hundreds of thousands of reasoning tokens. GPT 5.2: 9.8%, Gemini 3 Pro: 6.1%. 개별 step은 풀 수 있어도 전체 chain에서 무너짐 — 현재 reasoning 모델들의 long-horizon 한계 드러냄.</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>2026 벤치마크</t>
         </is>
       </c>
     </row>
